--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484180_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484180_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.265499999999999</v>
+        <v>8.5101</v>
       </c>
       <c r="E2" t="n">
-        <v>7.604</v>
+        <v>7.9328</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6614</v>
+        <v>0.5773</v>
       </c>
       <c r="G2" t="n">
         <v>7.9192</v>
@@ -610,13 +610,13 @@
         <v>1.5871</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2489</v>
+        <v>-0.0043</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.2947</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3746</v>
+        <v>0.2904</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.6115</v>
+        <v>6.3933</v>
       </c>
       <c r="E3" t="n">
-        <v>6.3255</v>
+        <v>6.3879</v>
       </c>
       <c r="F3" t="n">
-        <v>0.286</v>
+        <v>0.0055</v>
       </c>
       <c r="G3" t="n">
         <v>1.6245</v>
@@ -688,13 +688,13 @@
         <v>1.9838</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1222</v>
+        <v>0.904</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3912</v>
+        <v>0.4535</v>
       </c>
       <c r="U3" t="n">
-        <v>0.731</v>
+        <v>0.4505</v>
       </c>
       <c r="V3" t="n">
         <v>1.881</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.2501</v>
+        <v>3.9053</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5246</v>
+        <v>3.9554</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.2745</v>
+        <v>-0.0501</v>
       </c>
       <c r="G4" t="n">
         <v>1.8232</v>
@@ -766,13 +766,13 @@
         <v>1.5871</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.0293</v>
+        <v>-0.3741</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8105</v>
+        <v>-0.3797</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2188</v>
+        <v>0.0056</v>
       </c>
       <c r="V4" t="n">
         <v>0.8692</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3954</v>
+        <v>2.3949</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1237</v>
+        <v>1.7585</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2717</v>
+        <v>0.6364</v>
       </c>
       <c r="G5" t="n">
         <v>1.4866</v>
@@ -844,13 +844,13 @@
         <v>2.1822</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2897</v>
+        <v>0.7099</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4761</v>
+        <v>0.1588</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1864</v>
+        <v>0.5511</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. TEJERO CASASAYAS</t>
+          <t>A. CUMELLES CESPEDES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0255</v>
+        <v>0.6679</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6718</v>
+        <v>1.3432</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3537</v>
+        <v>-0.6754</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.0642</v>
+        <v>0.2709</v>
       </c>
       <c r="H6" t="n">
-        <v>1.9404</v>
+        <v>1.8398</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.0046</v>
+        <v>-1.5689</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7113</v>
+        <v>2.9939</v>
       </c>
       <c r="K6" t="n">
-        <v>2.5913</v>
+        <v>2.8332</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.8799</v>
+        <v>0.1606</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.7755</v>
+        <v>-2.7229</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6509</v>
+        <v>-0.9933999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.1246</v>
+        <v>-1.7295</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1822</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1822</v>
+        <v>1.9838</v>
       </c>
       <c r="S6" t="n">
-        <v>1.582</v>
+        <v>-0.08359999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6349</v>
+        <v>-0.1473</v>
       </c>
       <c r="U6" t="n">
-        <v>0.947</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6745</v>
+        <v>1.4724</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6745</v>
+        <v>1.4724</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. CUMELLES CESPEDES</t>
+          <t>A. LATORRE SEGURA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9436</v>
+        <v>0.6464</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4226</v>
+        <v>0.6667999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.479</v>
+        <v>-0.0204</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2709</v>
+        <v>0.2992</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8398</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.5689</v>
+        <v>0.2992</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9939</v>
+        <v>0.5648</v>
       </c>
       <c r="K7" t="n">
-        <v>2.8332</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1606</v>
+        <v>0.5648</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.7229</v>
+        <v>-0.2656</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9933999999999999</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7295</v>
+        <v>-0.2656</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9919</v>
+        <v>0.1984</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9838</v>
+        <v>0.1984</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1921</v>
+        <v>0.1488</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0679</v>
+        <v>0.102</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2601</v>
+        <v>0.0468</v>
       </c>
       <c r="V7" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. LATORRE SEGURA</t>
+          <t>E. TEJERO CASASAYAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5163</v>
+        <v>0.4397</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5648</v>
+        <v>0.4507</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0485</v>
+        <v>-0.011</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2992</v>
+        <v>-2.0642</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>1.9404</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2992</v>
+        <v>-4.0046</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5648</v>
+        <v>0.7113</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>2.5913</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5648</v>
+        <v>-1.8799</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2656</v>
+        <v>-2.7755</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.6509</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2656</v>
+        <v>-2.1246</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1984</v>
+        <v>2.1822</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1984</v>
+        <v>2.1822</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0187</v>
+        <v>0.9962</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.4139</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0187</v>
+        <v>0.5823</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.6745</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2155</v>
+        <v>-0.7413</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1754</v>
+        <v>-0.2101</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3909</v>
+        <v>-0.5312</v>
       </c>
       <c r="G9" t="n">
         <v>1.142</v>
@@ -1156,13 +1156,13 @@
         <v>2.3806</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2215</v>
+        <v>0.6957</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8843</v>
+        <v>0.4989</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3372</v>
+        <v>0.1969</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5633</v>
+        <v>-1.4424</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8625</v>
+        <v>-1.1063</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7008</v>
+        <v>-0.3361</v>
       </c>
       <c r="G10" t="n">
         <v>-1.7815</v>
@@ -1234,13 +1234,13 @@
         <v>2.1822</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.369</v>
+        <v>-0.248</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0679</v>
+        <v>-0.3117</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.301</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6032</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2759</v>
+        <v>-3.8856</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7799</v>
+        <v>-1.4738</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.496</v>
+        <v>-2.4119</v>
       </c>
       <c r="G11" t="n">
         <v>-2.5579</v>
@@ -1312,13 +1312,13 @@
         <v>0.5952</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3293</v>
+        <v>0.0609</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0227</v>
+        <v>0.3288</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.352</v>
+        <v>-0.2678</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>15.9532</v>
+        <v>16.8883</v>
       </c>
       <c r="E12" t="n">
-        <v>18.77</v>
+        <v>19.7051</v>
       </c>
       <c r="F12" t="n">
         <v>-2.8169</v>
@@ -1381,7 +1381,7 @@
         <v>-11.886</v>
       </c>
       <c r="P12" t="n">
-        <v>2.975799999999999</v>
+        <v>2.9758</v>
       </c>
       <c r="Q12" t="n">
         <v>-13.8868</v>
@@ -1390,10 +1390,10 @@
         <v>16.8626</v>
       </c>
       <c r="S12" t="n">
-        <v>1.8703</v>
+        <v>2.8055</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1127999999999999</v>
+        <v>0.8225000000000001</v>
       </c>
       <c r="U12" t="n">
         <v>1.9832</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.3225</v>
+        <v>2.4876</v>
       </c>
       <c r="E13" t="n">
-        <v>6.0923</v>
+        <v>5.378</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.7698</v>
+        <v>-2.8905</v>
       </c>
       <c r="G13" t="n">
         <v>1.677</v>
@@ -1468,13 +1468,13 @@
         <v>2.3806</v>
       </c>
       <c r="S13" t="n">
-        <v>1.586</v>
+        <v>0.7511</v>
       </c>
       <c r="T13" t="n">
-        <v>0.805</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7809</v>
+        <v>0.6602</v>
       </c>
       <c r="V13" t="n">
         <v>-0.3373</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7011</v>
+        <v>1.5787</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4005</v>
+        <v>1.5025</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3007</v>
+        <v>0.0762</v>
       </c>
       <c r="G14" t="n">
         <v>0.3601</v>
@@ -1546,13 +1546,13 @@
         <v>1.5871</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.246</v>
+        <v>-0.3684</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6858</v>
+        <v>-0.5838</v>
       </c>
       <c r="U14" t="n">
-        <v>0.4398</v>
+        <v>0.2153</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. MANYOSES ROCA</t>
+          <t>D. MARTIN VELA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.394</v>
+        <v>-1.1767</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.0242</v>
+        <v>0.7121</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3698</v>
+        <v>-1.8888</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.8995</v>
+        <v>-1.8644</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4486</v>
+        <v>-0.9225</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.4508</v>
+        <v>-0.9418</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1005</v>
+        <v>0.6044</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0202</v>
+        <v>0.4839</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0803</v>
+        <v>0.1205</v>
       </c>
       <c r="M18" t="n">
-        <v>-1</v>
+        <v>-2.4687</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4688</v>
+        <v>-1.4064</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5312</v>
+        <v>-1.0623</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1984</v>
+        <v>0.9919</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1984</v>
+        <v>0.9919</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.161</v>
+        <v>0.299</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1247</v>
+        <v>0.1077</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0363</v>
+        <v>0.1913</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.532</v>
+        <v>-0.6032</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.532</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. MARTIN VELA</t>
+          <t>M. MANYOSES ROCA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.7812</v>
+        <v>-1.2359</v>
       </c>
       <c r="E19" t="n">
-        <v>0.304</v>
+        <v>0.07779999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.0852</v>
+        <v>-1.3137</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.8644</v>
+        <v>-0.8995</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9225</v>
+        <v>-0.4486</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9418</v>
+        <v>-0.4508</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6044</v>
+        <v>0.1005</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4839</v>
+        <v>0.0202</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1205</v>
+        <v>0.0803</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.4687</v>
+        <v>-1</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4064</v>
+        <v>-0.4688</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.0623</v>
+        <v>-0.5312</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9919</v>
+        <v>0.1984</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9919</v>
+        <v>0.1984</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3055</v>
+        <v>-0.0028</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3004</v>
+        <v>-0.0227</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0051</v>
+        <v>0.0198</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6032</v>
+        <v>-0.532</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6032</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.7888</v>
+        <v>-1.6724</v>
       </c>
       <c r="E20" t="n">
-        <v>1.3793</v>
+        <v>2.1956</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.1681</v>
+        <v>-3.868</v>
       </c>
       <c r="G20" t="n">
         <v>0.1221</v>
@@ -2014,13 +2014,13 @@
         <v>2.579</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3076</v>
+        <v>-0.1913</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.2979</v>
+        <v>-0.4817</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0097</v>
+        <v>0.2904</v>
       </c>
       <c r="V20" t="n">
         <v>-1.2065</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.81</v>
+        <v>-2.8236</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4485</v>
+        <v>-0.9586</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3615</v>
+        <v>-1.865</v>
       </c>
       <c r="G21" t="n">
         <v>-0.7665999999999999</v>
@@ -2092,13 +2092,13 @@
         <v>1.3887</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1904</v>
+        <v>-0.204</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2382</v>
+        <v>-0.272</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4286</v>
+        <v>0.0679</v>
       </c>
       <c r="V21" t="n">
         <v>-0.266</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2415</v>
+        <v>-3.7014</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3524</v>
+        <v>-1.1686</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.889</v>
+        <v>-2.5328</v>
       </c>
       <c r="G22" t="n">
         <v>-1.3</v>
@@ -2170,13 +2170,13 @@
         <v>1.7855</v>
       </c>
       <c r="S22" t="n">
-        <v>0.844</v>
+        <v>0.3841</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9921</v>
+        <v>0.1758</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.148</v>
+        <v>0.2082</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6032</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.099</v>
+        <v>-6.1867</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4879</v>
+        <v>-2.8757</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.6111</v>
+        <v>-3.3109</v>
       </c>
       <c r="G23" t="n">
         <v>-4.4221</v>
@@ -2248,13 +2248,13 @@
         <v>2.1822</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.4947</v>
+        <v>-0.5824</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2356</v>
+        <v>-0.6234</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2591</v>
+        <v>0.041</v>
       </c>
       <c r="V23" t="n">
         <v>0.6032</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-15.9532</v>
+        <v>-14.5927</v>
       </c>
       <c r="E24" t="n">
         <v>2.8169</v>
       </c>
       <c r="F24" t="n">
-        <v>-18.7699</v>
+        <v>-17.4096</v>
       </c>
       <c r="G24" t="n">
         <v>-8.162100000000001</v>
@@ -2296,7 +2296,7 @@
         <v>-12.826</v>
       </c>
       <c r="I24" t="n">
-        <v>4.664099999999999</v>
+        <v>4.6641</v>
       </c>
       <c r="J24" t="n">
         <v>21.468</v>
@@ -2326,13 +2326,13 @@
         <v>13.887</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.8704</v>
+        <v>-0.5099</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.9832</v>
+        <v>-1.9834</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1128000000000001</v>
+        <v>1.473</v>
       </c>
       <c r="V24" t="n">
         <v>-2.944999999999999</v>
